--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202606/Category_P&L_20260609.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202606/Category_P&L_20260609.xlsx
@@ -43549,28 +43549,28 @@
         <v>46181</v>
       </c>
       <c r="B1136">
-        <v>92818575.01000001</v>
+        <v>93791423.37</v>
       </c>
       <c r="C1136">
-        <v>-5710050.85</v>
+        <v>996050.13</v>
       </c>
       <c r="D1136">
-        <v>-0.061518</v>
+        <v>0.010731</v>
       </c>
       <c r="E1136">
-        <v>14342.37</v>
+        <v>4877.12</v>
       </c>
       <c r="F1136">
-        <v>0.000155</v>
+        <v>5.3E-05</v>
       </c>
       <c r="G1136">
-        <v>-59028.36</v>
+        <v>4929.38</v>
       </c>
       <c r="H1136">
-        <v>-0.000636</v>
+        <v>5.3E-05</v>
       </c>
       <c r="I1136">
-        <v>-1.32</v>
+        <v>-0.99</v>
       </c>
       <c r="J1136">
         <v>0</v>
@@ -43593,13 +43593,13 @@
         <v>-628570.21</v>
       </c>
       <c r="D1137">
-        <v>-0.006772</v>
+        <v>-0.006702</v>
       </c>
       <c r="E1137">
         <v>4907.54</v>
       </c>
       <c r="F1137">
-        <v>5.3E-05</v>
+        <v>5.2E-05</v>
       </c>
       <c r="G1137">
         <v>62</v>
